--- a/Скрипты/data/Спецификация_АБК.xlsx
+++ b/Скрипты/data/Спецификация_АБК.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\работа альтэн\ЦВСИГ\ЦСВИГ ИСПОЛН\ЦСВИГ ИСПОЛН (1)\АБК\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66507AC4-A106-4445-8BC1-58DC87DBFEB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF9E082A-944C-4888-881B-DDC13879F7B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Сводная изделий" sheetId="3" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="86">
   <si>
     <t>№</t>
   </si>
@@ -1970,7 +1970,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA7DE141-0CEB-4EE3-BAAE-81328705A9B4}">
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultRowHeight="14.6"/>
   <cols>
     <col min="1" max="1" width="7.4609375" customWidth="1"/>
@@ -1978,59 +1978,61 @@
     <col min="3" max="3" width="15.84375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" ht="15.9">
-      <c r="A1" s="7">
-        <v>1</v>
-      </c>
-      <c r="B1" s="8" t="s">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="31.75">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="1" customFormat="1" ht="15.9">
+      <c r="A2" s="7">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" s="1" customFormat="1" ht="31.75">
-      <c r="A2" s="7">
+      <c r="C2" s="9"/>
+      <c r="D2" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="1" customFormat="1" ht="31.75">
+      <c r="A3" s="7">
         <v>2</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D3" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="12">
         <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" s="1" customFormat="1" ht="15.9">
-      <c r="A3" s="7">
-        <v>3</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="12">
-        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="1" customFormat="1" ht="15.9">
       <c r="A4" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="12" t="s">
@@ -2042,40 +2044,40 @@
     </row>
     <row r="5" spans="1:10" s="1" customFormat="1" ht="15.9">
       <c r="A5" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="12" t="s">
         <v>3</v>
       </c>
       <c r="E5" s="12">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="1" customFormat="1" ht="15.9">
       <c r="A6" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="12" t="s">
         <v>3</v>
       </c>
       <c r="E6" s="12">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="1" customFormat="1" ht="15.9">
       <c r="A7" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="12" t="s">
@@ -2085,97 +2087,95 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" s="1" customFormat="1" ht="47.6">
+    <row r="8" spans="1:10" s="1" customFormat="1" ht="15.9">
       <c r="A8" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="12" t="s">
         <v>3</v>
       </c>
       <c r="E8" s="12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" s="1" customFormat="1" ht="15.9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" s="1" customFormat="1" ht="47.6">
       <c r="A9" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="12" t="s">
         <v>3</v>
       </c>
       <c r="E9" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="1" customFormat="1" ht="15.9">
       <c r="A10" s="7">
-        <v>10</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="14">
-        <v>15</v>
-      </c>
-      <c r="F10" s="5"/>
+        <v>9</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="12">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:10" s="1" customFormat="1" ht="15.9">
       <c r="A11" s="7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E11" s="14">
-        <v>2</v>
-      </c>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
+        <v>15</v>
+      </c>
+      <c r="F11" s="5"/>
     </row>
     <row r="12" spans="1:10" s="1" customFormat="1" ht="15.9">
       <c r="A12" s="7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>10</v>
+        <v>47</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>3</v>
       </c>
       <c r="E12" s="14">
-        <v>130</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
     </row>
     <row r="13" spans="1:10" s="1" customFormat="1" ht="15.9">
       <c r="A13" s="7">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>48</v>
@@ -2184,137 +2184,154 @@
         <v>10</v>
       </c>
       <c r="E13" s="14">
-        <v>168</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="1" customFormat="1" ht="15.9">
       <c r="A14" s="7">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="14" t="s">
         <v>10</v>
       </c>
       <c r="E14" s="14">
-        <v>15</v>
+        <v>204</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="1" customFormat="1" ht="15.9">
       <c r="A15" s="7">
+        <v>14</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="14">
         <v>15</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="12">
-        <v>600</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="1" customFormat="1" ht="15.9">
       <c r="A16" s="7">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E16" s="12">
-        <v>313</v>
+        <v>600</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="1" customFormat="1" ht="15.9">
       <c r="A17" s="7">
-        <v>17</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="13">
-        <v>1</v>
+        <v>16</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="12">
+        <v>313</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="1" customFormat="1" ht="15.9">
       <c r="A18" s="7">
-        <v>18</v>
-      </c>
-      <c r="B18" s="47" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" s="47" t="s">
-        <v>79</v>
-      </c>
-      <c r="D18" s="48" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18" s="49">
+        <v>17</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="1" customFormat="1" ht="15.9">
       <c r="A19" s="7">
-        <v>19</v>
-      </c>
-      <c r="B19" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="C19" s="51" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="47" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" s="47" t="s">
         <v>79</v>
       </c>
-      <c r="D19" s="52" t="s">
-        <v>3</v>
-      </c>
-      <c r="E19" s="53">
+      <c r="D19" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="E19" s="49">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5" s="1" customFormat="1" ht="15.9">
       <c r="A20" s="7">
+        <v>19</v>
+      </c>
+      <c r="B20" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="D20" s="52" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" s="1" customFormat="1" ht="15.9">
+      <c r="A21" s="7">
         <v>20</v>
       </c>
-      <c r="B20" s="47" t="s">
+      <c r="B21" s="47" t="s">
         <v>81</v>
       </c>
-      <c r="C20" s="47" t="s">
+      <c r="C21" s="47" t="s">
         <v>82</v>
       </c>
-      <c r="D20" s="48" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="49">
+      <c r="D21" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="49">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="I11:J11">
+  <conditionalFormatting sqref="I12:J12">
     <cfRule type="expression" dxfId="5" priority="1">
-      <formula>I11&lt;&gt;"OK"</formula>
+      <formula>I12&lt;&gt;"OK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J11">
+  <conditionalFormatting sqref="J12">
     <cfRule type="expression" dxfId="4" priority="2">
-      <formula>J11&lt;&gt;"OK"</formula>
+      <formula>J12&lt;&gt;"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2323,7 +2340,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{242A7168-0A52-4DEC-B8E6-15E5D4AD677B}">
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr defaultRowHeight="14.6"/>
   <cols>
     <col min="2" max="2" width="72.921875" customWidth="1"/>
@@ -2332,26 +2349,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" ht="31.75">
-      <c r="A1" s="7">
-        <v>1</v>
-      </c>
-      <c r="B1" s="8" t="s">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="1" customFormat="1" ht="31.75">
+      <c r="A2" s="7">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" s="1" customFormat="1" ht="47.6">
-      <c r="A2" s="7">
-        <v>2</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>4</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="12" t="s">
@@ -2361,12 +2380,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="1" customFormat="1" ht="15.9">
+    <row r="3" spans="1:10" s="1" customFormat="1" ht="47.6">
       <c r="A3" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="12" t="s">
@@ -2378,10 +2397,10 @@
     </row>
     <row r="4" spans="1:10" s="1" customFormat="1" ht="15.9">
       <c r="A4" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="12" t="s">
@@ -2393,10 +2412,10 @@
     </row>
     <row r="5" spans="1:10" s="1" customFormat="1" ht="15.9">
       <c r="A5" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="12" t="s">
@@ -2406,12 +2425,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="1" customFormat="1" ht="31.75">
+    <row r="6" spans="1:10" s="1" customFormat="1" ht="15.9">
       <c r="A6" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="12" t="s">
@@ -2421,12 +2440,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:10" s="1" customFormat="1" ht="15.9">
+    <row r="7" spans="1:10" s="1" customFormat="1" ht="31.75">
       <c r="A7" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="12" t="s">
@@ -2438,201 +2457,216 @@
     </row>
     <row r="8" spans="1:10" s="1" customFormat="1" ht="15.9">
       <c r="A8" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="12" t="s">
         <v>3</v>
       </c>
       <c r="E8" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="1" customFormat="1" ht="15.9">
       <c r="A9" s="7">
-        <v>9</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="14">
-        <v>2</v>
-      </c>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
+        <v>8</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="9"/>
+      <c r="D9" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="12">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:10" s="1" customFormat="1" ht="15.9">
       <c r="A10" s="7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>10</v>
+        <v>47</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>3</v>
       </c>
       <c r="E10" s="14">
         <v>2</v>
       </c>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
     </row>
     <row r="11" spans="1:10" s="1" customFormat="1" ht="15.9">
       <c r="A11" s="7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="14" t="s">
         <v>10</v>
       </c>
       <c r="E11" s="14">
-        <v>150</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="1" customFormat="1" ht="15.9">
       <c r="A12" s="7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E12" s="14">
-        <v>3</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="1" customFormat="1" ht="15.9">
       <c r="A13" s="7">
+        <v>12</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" s="1" customFormat="1" ht="15.9">
+      <c r="A14" s="7">
         <v>13</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B14" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C14" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="E13" s="12">
+      <c r="D14" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="12">
         <v>300</v>
       </c>
     </row>
-    <row r="14" spans="1:10" s="1" customFormat="1" ht="31.75">
-      <c r="A14" s="7">
+    <row r="15" spans="1:10" s="1" customFormat="1" ht="31.75">
+      <c r="A15" s="7">
         <v>14</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B15" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C15" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="12">
+      <c r="D15" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="12">
         <v>150</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" s="1" customFormat="1" ht="15.9">
-      <c r="A15" s="7">
-        <v>15</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="13">
-        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="1" customFormat="1" ht="15.9">
       <c r="A16" s="7">
-        <v>16</v>
-      </c>
-      <c r="B16" s="54" t="s">
-        <v>78</v>
-      </c>
-      <c r="C16" s="54" t="s">
-        <v>79</v>
-      </c>
-      <c r="D16" s="59" t="s">
-        <v>3</v>
-      </c>
-      <c r="E16" s="55">
+        <v>15</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="1" customFormat="1" ht="15.9">
       <c r="A17" s="7">
-        <v>17</v>
-      </c>
-      <c r="B17" s="56" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" s="57" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="54" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="54" t="s">
         <v>79</v>
       </c>
-      <c r="D17" s="60" t="s">
-        <v>3</v>
-      </c>
-      <c r="E17" s="58">
+      <c r="D17" s="59" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="55">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="1" customFormat="1" ht="15.9">
       <c r="A18" s="7">
+        <v>17</v>
+      </c>
+      <c r="B18" s="56" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" s="57" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" s="60" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="1" customFormat="1" ht="15.9">
+      <c r="A19" s="7">
         <v>18</v>
       </c>
-      <c r="B18" s="54" t="s">
+      <c r="B19" s="54" t="s">
         <v>81</v>
       </c>
-      <c r="C18" s="54" t="s">
+      <c r="C19" s="54" t="s">
         <v>82</v>
       </c>
-      <c r="D18" s="59" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18" s="55">
+      <c r="D19" s="59" t="s">
+        <v>3</v>
+      </c>
+      <c r="E19" s="55">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="I9:J9">
+  <conditionalFormatting sqref="I10:J10">
     <cfRule type="expression" dxfId="3" priority="1">
-      <formula>I9&lt;&gt;"OK"</formula>
+      <formula>I10&lt;&gt;"OK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J9">
+  <conditionalFormatting sqref="J10">
     <cfRule type="expression" dxfId="2" priority="2">
-      <formula>J9&lt;&gt;"OK"</formula>
+      <formula>J10&lt;&gt;"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2641,34 +2675,36 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A487A898-58A7-4B51-9A83-C34D1A06AD75}">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="14.6"/>
   <cols>
     <col min="2" max="2" width="75.61328125" customWidth="1"/>
     <col min="3" max="3" width="32.921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" ht="15.9">
-      <c r="A1" s="7">
-        <v>1</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="12">
-        <v>1</v>
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="31.75">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="1" customFormat="1" ht="15.9">
       <c r="A2" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="12" t="s">
@@ -2680,57 +2716,55 @@
     </row>
     <row r="3" spans="1:6" s="1" customFormat="1" ht="15.9">
       <c r="A3" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="12" t="s">
         <v>3</v>
       </c>
       <c r="E3" s="12">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" s="1" customFormat="1" ht="31.75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" s="1" customFormat="1" ht="15.9">
       <c r="A4" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="12" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" s="1" customFormat="1" ht="15.9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" s="1" customFormat="1" ht="31.75">
       <c r="A5" s="7">
-        <v>5</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="14">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="12">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:6" s="1" customFormat="1" ht="15.9">
       <c r="A6" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>54</v>
@@ -2739,70 +2773,70 @@
         <v>10</v>
       </c>
       <c r="E6" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:6" s="1" customFormat="1" ht="15.9">
       <c r="A7" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="14">
-        <v>96</v>
-      </c>
-      <c r="F7" s="5"/>
+        <v>6</v>
+      </c>
     </row>
     <row r="8" spans="1:6" s="1" customFormat="1" ht="15.9">
       <c r="A8" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D8" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E8" s="14">
-        <v>25</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="F8" s="5"/>
     </row>
     <row r="9" spans="1:6" s="1" customFormat="1" ht="15.9">
       <c r="A9" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E9" s="14">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:6" s="1" customFormat="1" ht="15.9">
       <c r="A10" s="7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D10" s="13" t="s">
         <v>3</v>
@@ -2813,13 +2847,13 @@
     </row>
     <row r="11" spans="1:6" s="1" customFormat="1" ht="15.9">
       <c r="A11" s="7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D11" s="13" t="s">
         <v>3</v>
@@ -2830,221 +2864,238 @@
     </row>
     <row r="12" spans="1:6" s="1" customFormat="1" ht="15.9">
       <c r="A12" s="7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="D12" s="13" t="s">
         <v>3</v>
       </c>
       <c r="E12" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:6" s="1" customFormat="1" ht="15.9">
       <c r="A13" s="7">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>3</v>
       </c>
       <c r="E13" s="14">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="1" customFormat="1" ht="15.9">
       <c r="A14" s="7">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="13">
-        <v>2</v>
+      <c r="E14" s="14">
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:6" s="1" customFormat="1" ht="15.9">
       <c r="A15" s="7">
-        <v>15</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="12">
+        <v>14</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:6" s="1" customFormat="1" ht="15.9">
       <c r="A16" s="7">
-        <v>16</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="14">
-        <v>95</v>
+        <v>15</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="9"/>
+      <c r="D16" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="12">
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:6" s="1" customFormat="1" ht="15.9">
       <c r="A17" s="7">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E17" s="14">
-        <v>578</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:6" s="1" customFormat="1" ht="15.9">
       <c r="A18" s="7">
+        <v>17</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="14">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" s="1" customFormat="1" ht="15.9">
+      <c r="A19" s="7">
         <v>18</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B19" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C19" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18" s="12">
+      <c r="D19" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="E19" s="12">
         <v>800</v>
       </c>
     </row>
-    <row r="19" spans="1:6" s="1" customFormat="1" ht="31.75">
-      <c r="A19" s="7">
+    <row r="20" spans="1:6" s="1" customFormat="1" ht="31.75">
+      <c r="A20" s="7">
         <v>19</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B20" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C20" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" s="12">
+      <c r="D20" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="12">
         <v>400</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" s="1" customFormat="1" ht="15.9">
-      <c r="A20" s="7">
-        <v>20</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E20" s="13">
-        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:6" s="1" customFormat="1" ht="15.9">
       <c r="A21" s="7">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="D21" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="E21" s="14">
-        <v>96</v>
-      </c>
-      <c r="F21" s="5"/>
+      <c r="E21" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="1:6" s="1" customFormat="1" ht="15.9">
       <c r="A22" s="7">
-        <v>22</v>
-      </c>
-      <c r="B22" s="54" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" s="54" t="s">
-        <v>79</v>
-      </c>
-      <c r="D22" s="59" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22" s="55">
-        <v>1</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="14">
+        <v>96</v>
+      </c>
+      <c r="F22" s="5"/>
     </row>
     <row r="23" spans="1:6" s="1" customFormat="1" ht="15.9">
       <c r="A23" s="7">
-        <v>23</v>
-      </c>
-      <c r="B23" s="56" t="s">
-        <v>80</v>
-      </c>
-      <c r="C23" s="57" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="54" t="s">
+        <v>78</v>
+      </c>
+      <c r="C23" s="54" t="s">
         <v>79</v>
       </c>
-      <c r="D23" s="60" t="s">
-        <v>3</v>
-      </c>
-      <c r="E23" s="58">
+      <c r="D23" s="59" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="55">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:6" s="1" customFormat="1" ht="15.9">
       <c r="A24" s="7">
+        <v>23</v>
+      </c>
+      <c r="B24" s="56" t="s">
+        <v>80</v>
+      </c>
+      <c r="C24" s="57" t="s">
+        <v>79</v>
+      </c>
+      <c r="D24" s="60" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" s="1" customFormat="1" ht="15.9">
+      <c r="A25" s="7">
         <v>24</v>
       </c>
-      <c r="B24" s="54" t="s">
+      <c r="B25" s="54" t="s">
         <v>81</v>
       </c>
-      <c r="C24" s="54" t="s">
+      <c r="C25" s="54" t="s">
         <v>82</v>
       </c>
-      <c r="D24" s="59" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="55">
+      <c r="D25" s="59" t="s">
+        <v>3</v>
+      </c>
+      <c r="E25" s="55">
         <v>1</v>
       </c>
     </row>
@@ -3055,7 +3106,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFA2FCBE-7F72-4F59-9D19-3FE23FC85E49}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="14.6"/>
   <cols>
     <col min="1" max="1" width="13.07421875" customWidth="1"/>
@@ -3066,46 +3117,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" ht="31.75">
-      <c r="A1" s="7">
-        <v>1</v>
-      </c>
-      <c r="B1" s="8" t="s">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" s="1" customFormat="1" ht="31.75">
+      <c r="A2" s="7">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" s="1" customFormat="1" ht="15.9">
-      <c r="A2" s="7">
-        <v>2</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>18</v>
-      </c>
+      <c r="C2" s="9"/>
       <c r="D2" s="12" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="12">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="1" customFormat="1" ht="15.9">
       <c r="A3" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>3</v>
@@ -3114,31 +3165,31 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:5" s="1" customFormat="1" ht="31.75">
+    <row r="4" spans="1:5" s="1" customFormat="1" ht="15.9">
       <c r="A4" s="7">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="1" customFormat="1" ht="31.75">
+      <c r="A5" s="7">
         <v>4</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B5" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" s="1" customFormat="1" ht="15.9">
-      <c r="A5" s="7">
-        <v>5</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>42</v>
-      </c>
+      <c r="C5" s="9"/>
       <c r="D5" s="12" t="s">
         <v>3</v>
       </c>
@@ -3148,154 +3199,171 @@
     </row>
     <row r="6" spans="1:5" s="1" customFormat="1" ht="15.9">
       <c r="A6" s="7">
-        <v>6</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="14">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="1" customFormat="1" ht="15.9">
       <c r="A7" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="13">
-        <v>15</v>
+      <c r="E7" s="14">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="1" customFormat="1" ht="15.9">
       <c r="A8" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="14">
-        <v>200</v>
+        <v>3</v>
+      </c>
+      <c r="E8" s="13">
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="1" customFormat="1" ht="15.9">
       <c r="A9" s="7">
-        <v>9</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="12">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="14">
         <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="1" customFormat="1" ht="15.9">
       <c r="A10" s="7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E10" s="12">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="1" customFormat="1" ht="15.9">
       <c r="A11" s="7">
-        <v>11</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="13">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="12">
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="1" customFormat="1" ht="15.9">
       <c r="A12" s="7">
-        <v>12</v>
-      </c>
-      <c r="B12" s="54" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" s="54" t="s">
-        <v>79</v>
-      </c>
-      <c r="D12" s="59" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="55">
+        <v>11</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="1" customFormat="1" ht="15.9">
       <c r="A13" s="7">
-        <v>13</v>
-      </c>
-      <c r="B13" s="56" t="s">
-        <v>80</v>
-      </c>
-      <c r="C13" s="57" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="54" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="54" t="s">
         <v>79</v>
       </c>
-      <c r="D13" s="60" t="s">
-        <v>3</v>
-      </c>
-      <c r="E13" s="58">
+      <c r="D13" s="59" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" s="55">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="1" customFormat="1" ht="15.9">
       <c r="A14" s="7">
+        <v>13</v>
+      </c>
+      <c r="B14" s="56" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" s="57" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" s="60" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" s="1" customFormat="1" ht="15.9">
+      <c r="A15" s="7">
         <v>14</v>
       </c>
-      <c r="B14" s="54" t="s">
+      <c r="B15" s="54" t="s">
         <v>81</v>
       </c>
-      <c r="C14" s="54" t="s">
+      <c r="C15" s="54" t="s">
         <v>82</v>
       </c>
-      <c r="D14" s="59" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="55">
+      <c r="D15" s="59" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="55">
         <v>1</v>
       </c>
     </row>
@@ -3306,7 +3374,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{696B478E-05AD-40B7-B6C0-C1484602A77C}">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr defaultRowHeight="14.6"/>
   <cols>
     <col min="2" max="2" width="61.61328125" bestFit="1" customWidth="1"/>
@@ -3315,116 +3383,118 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="1" customFormat="1" ht="31.75">
-      <c r="A1" s="7">
-        <v>1</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="12">
-        <v>18</v>
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" ht="31.75">
       <c r="A2" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="12" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" s="1" customFormat="1" ht="15.9">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="1" customFormat="1" ht="31.75">
       <c r="A3" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="12" t="s">
         <v>3</v>
       </c>
       <c r="E3" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="1" customFormat="1" ht="15.9">
       <c r="A4" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="12" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="12">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" s="1" customFormat="1" ht="47.6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" s="1" customFormat="1" ht="15.9">
       <c r="A5" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="12" t="s">
         <v>3</v>
       </c>
       <c r="E5" s="12">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" s="1" customFormat="1" ht="15.9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="1" customFormat="1" ht="47.6">
       <c r="A6" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="12" t="s">
         <v>3</v>
       </c>
       <c r="E6" s="12">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="1" customFormat="1" ht="15.9">
       <c r="A7" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="12" t="s">
         <v>3</v>
       </c>
       <c r="E7" s="12">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="1" customFormat="1" ht="15.9">
       <c r="A8" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="12" t="s">
@@ -3436,97 +3506,95 @@
     </row>
     <row r="9" spans="1:10" s="1" customFormat="1" ht="15.9">
       <c r="A9" s="7">
-        <v>9</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="14">
-        <v>1</v>
-      </c>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
+        <v>8</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="9"/>
+      <c r="D9" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="12">
+        <v>2</v>
+      </c>
     </row>
     <row r="10" spans="1:10" s="1" customFormat="1" ht="15.9">
       <c r="A10" s="7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="14">
+        <v>1</v>
+      </c>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+    </row>
+    <row r="11" spans="1:10" s="1" customFormat="1" ht="15.9">
+      <c r="A11" s="7">
+        <v>10</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C11" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="14">
+      <c r="D11" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="14">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:10" s="1" customFormat="1" ht="31.75">
-      <c r="A11" s="7">
+    <row r="12" spans="1:10" s="1" customFormat="1" ht="31.75">
+      <c r="A12" s="7">
         <v>11</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B12" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" s="1" customFormat="1" ht="15.9">
-      <c r="A12" s="7">
-        <v>12</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>57</v>
-      </c>
+      <c r="C12" s="10"/>
       <c r="D12" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="14">
-        <v>35</v>
-      </c>
-      <c r="F12" s="5"/>
+        <v>3</v>
+      </c>
+      <c r="E12" s="13">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:10" s="1" customFormat="1" ht="15.9">
       <c r="A13" s="7">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="D13" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="13" t="s">
         <v>10</v>
       </c>
       <c r="E13" s="14">
-        <v>396</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="F13" s="5"/>
     </row>
     <row r="14" spans="1:10" s="1" customFormat="1" ht="15.9">
       <c r="A14" s="7">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>48</v>
@@ -3535,103 +3603,120 @@
         <v>10</v>
       </c>
       <c r="E14" s="14">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" s="1" customFormat="1" ht="15.9">
+      <c r="A15" s="7">
+        <v>14</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="11" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" s="1" customFormat="1" ht="31.75">
-      <c r="A15" s="7">
-        <v>15</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="12">
-        <v>500</v>
+      <c r="D15" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="14">
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="1" customFormat="1" ht="31.75">
       <c r="A16" s="7">
+        <v>15</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="12">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" s="1" customFormat="1" ht="31.75">
+      <c r="A17" s="7">
         <v>16</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B17" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C17" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="12">
+      <c r="D17" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="12">
         <v>400</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" s="1" customFormat="1" ht="15.9">
-      <c r="A17" s="7">
-        <v>17</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="13">
-        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="1" customFormat="1" ht="15.9">
       <c r="A18" s="7">
-        <v>18</v>
-      </c>
-      <c r="B18" s="56" t="s">
-        <v>80</v>
-      </c>
-      <c r="C18" s="57" t="s">
-        <v>79</v>
-      </c>
-      <c r="D18" s="60" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18" s="58">
+        <v>17</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5" s="1" customFormat="1" ht="15.9">
       <c r="A19" s="7">
+        <v>18</v>
+      </c>
+      <c r="B19" s="56" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" s="57" t="s">
+        <v>79</v>
+      </c>
+      <c r="D19" s="60" t="s">
+        <v>3</v>
+      </c>
+      <c r="E19" s="58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" s="1" customFormat="1" ht="15.9">
+      <c r="A20" s="7">
         <v>19</v>
       </c>
-      <c r="B19" s="54" t="s">
+      <c r="B20" s="54" t="s">
         <v>81</v>
       </c>
-      <c r="C19" s="54" t="s">
+      <c r="C20" s="54" t="s">
         <v>82</v>
       </c>
-      <c r="D19" s="59" t="s">
-        <v>3</v>
-      </c>
-      <c r="E19" s="55">
+      <c r="D20" s="59" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="55">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="I9:J9">
+  <conditionalFormatting sqref="I10:J10">
     <cfRule type="expression" dxfId="1" priority="1">
-      <formula>I9&lt;&gt;"OK"</formula>
+      <formula>I10&lt;&gt;"OK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J9">
+  <conditionalFormatting sqref="J10">
     <cfRule type="expression" dxfId="0" priority="2">
-      <formula>J9&lt;&gt;"OK"</formula>
+      <formula>J10&lt;&gt;"OK"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
